--- a/artfynd/A 42635-2025 artfynd.xlsx
+++ b/artfynd/A 42635-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103464256</v>
+        <v>111929377</v>
       </c>
       <c r="B2" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85534</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>241</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Alb. &amp; Schwein.) Shear</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,17 +709,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nedre Sundet, Vstm</t>
+          <t>Bornsviken, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523332.4633416774</v>
+        <v>523350</v>
       </c>
       <c r="R2" t="n">
-        <v>6619802.37170042</v>
+        <v>6619533</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-09-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,12 +779,7 @@
         <v>111286442</v>
       </c>
       <c r="B3" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -842,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523158.5437745763</v>
+        <v>523159</v>
       </c>
       <c r="R3" t="n">
-        <v>6619732.675472289</v>
+        <v>6619733</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,19 +855,9 @@
           <t>2023-08-03</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,37 +885,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111350581</v>
+        <v>121150986</v>
       </c>
       <c r="B4" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -953,26 +918,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bornsviken, Vstm</t>
+          <t>Morskoga, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523216.6034484834</v>
+        <v>523153</v>
       </c>
       <c r="R4" t="n">
-        <v>6619742.117365031</v>
+        <v>6619792</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,22 +954,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,34 +973,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Ahlqvist</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111350516</v>
+        <v>112792336</v>
       </c>
       <c r="B5" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1055,26 +1002,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1090,13 +1037,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523319.7728949333</v>
+        <v>523332</v>
       </c>
       <c r="R5" t="n">
-        <v>6619811.373445455</v>
+        <v>6619704</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,22 +1067,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,42 +1100,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111350555</v>
+        <v>119371856</v>
       </c>
       <c r="B6" t="n">
-        <v>89369</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93216</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Brödtaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum versipelle</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1206,21 +1138,24 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bornsviken, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523345.6244904655</v>
+        <v>523350</v>
       </c>
       <c r="R6" t="n">
-        <v>6619798.922468832</v>
+        <v>6619533</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1244,22 +1179,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2024-08-01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1268,7 +1203,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1287,37 +1221,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111658509</v>
+        <v>103464256</v>
       </c>
       <c r="B7" t="n">
-        <v>90678</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1326,17 +1255,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bornsviken, Vstm</t>
+          <t>Nedre Sundet, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523154</v>
+        <v>523332</v>
       </c>
       <c r="R7" t="n">
-        <v>6619785</v>
+        <v>6619803</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1360,12 +1289,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
+          <t>2022-09-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1393,37 +1322,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111658400</v>
+        <v>111660362</v>
       </c>
       <c r="B8" t="n">
-        <v>90295</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4740</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sotriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius lignyotus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1436,10 +1360,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523326</v>
+        <v>523381</v>
       </c>
       <c r="R8" t="n">
-        <v>6619778</v>
+        <v>6619759</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1466,12 +1390,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2022-08-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-23</t>
+          <t>2022-08-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,43 +1423,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111660445</v>
+        <v>111660401</v>
       </c>
       <c r="B9" t="n">
-        <v>95532</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1543,10 +1461,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523338</v>
+        <v>523379</v>
       </c>
       <c r="R9" t="n">
-        <v>6619822</v>
+        <v>6619784</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1573,12 +1491,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-08-23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-08-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>gamla kroppar, en ny på gång</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,19 +1529,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111660362</v>
+        <v>112280400</v>
       </c>
       <c r="B10" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1639,8 +1557,16 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1649,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523381</v>
+        <v>523134</v>
       </c>
       <c r="R10" t="n">
-        <v>6619759</v>
+        <v>6619885</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1679,12 +1605,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-08-20</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-08-20</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,15 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111744446</v>
+        <v>112280409</v>
       </c>
       <c r="B11" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1728,39 +1649,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1768,10 +1676,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523374</v>
+        <v>523127</v>
       </c>
       <c r="R11" t="n">
-        <v>6619501</v>
+        <v>6619863</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1798,12 +1706,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-04-08</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,6 +1720,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1830,15 +1739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111929377</v>
+        <v>111658509</v>
       </c>
       <c r="B12" t="n">
-        <v>83506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1846,21 +1750,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>241</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1873,10 +1777,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523350</v>
+        <v>523154</v>
       </c>
       <c r="R12" t="n">
-        <v>6619533</v>
+        <v>6619785</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1903,12 +1807,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-09-05</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,49 +1840,36 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111940426</v>
+        <v>112280348</v>
       </c>
       <c r="B13" t="n">
-        <v>90835</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>4366</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -1987,10 +1878,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523334</v>
+        <v>523209</v>
       </c>
       <c r="R13" t="n">
-        <v>6619818</v>
+        <v>6619782</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2017,12 +1908,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-09-06</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,15 +1941,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112299854</v>
+        <v>112279685</v>
       </c>
       <c r="B14" t="n">
-        <v>89155</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2066,25 +1952,33 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5754</v>
+        <v>4404</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2093,10 +1987,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523148</v>
+        <v>523329</v>
       </c>
       <c r="R14" t="n">
-        <v>6619802</v>
+        <v>6619824</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2123,12 +2017,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,15 +2050,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112299375</v>
+        <v>112279929</v>
       </c>
       <c r="B15" t="n">
-        <v>90898</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2172,25 +2061,33 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5448</v>
+        <v>4404</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2199,10 +2096,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523136</v>
+        <v>523385</v>
       </c>
       <c r="R15" t="n">
-        <v>6619879</v>
+        <v>6619779</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2229,12 +2126,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2262,15 +2159,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112279968</v>
+        <v>112280330</v>
       </c>
       <c r="B16" t="n">
-        <v>90898</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2278,21 +2170,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5448</v>
+        <v>4404</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2305,10 +2197,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523344</v>
+        <v>523222</v>
       </c>
       <c r="R16" t="n">
-        <v>6619785</v>
+        <v>6619790</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2335,12 +2227,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2368,42 +2260,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>112280307</v>
+        <v>112792203</v>
       </c>
       <c r="B17" t="n">
-        <v>90876</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>4404</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2419,10 +2306,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523247</v>
+        <v>523123</v>
       </c>
       <c r="R17" t="n">
-        <v>6619802</v>
+        <v>6619838</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2449,17 +2336,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ring</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,15 +2369,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>112299094</v>
+        <v>111658400</v>
       </c>
       <c r="B18" t="n">
-        <v>89558</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92836</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2503,21 +2380,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>4740</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Sotriska</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius lignyotus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2530,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523332</v>
+        <v>523326</v>
       </c>
       <c r="R18" t="n">
-        <v>6619814</v>
+        <v>6619778</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2560,12 +2437,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-08-23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-09-22</t>
+          <t>2023-08-23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2593,15 +2470,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112280409</v>
+        <v>111350516</v>
       </c>
       <c r="B19" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2609,25 +2481,33 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
@@ -2636,13 +2516,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523127</v>
+        <v>523320</v>
       </c>
       <c r="R19" t="n">
-        <v>6619863</v>
+        <v>6619811</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2666,12 +2546,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2699,15 +2579,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112280348</v>
+        <v>111350555</v>
       </c>
       <c r="B20" t="n">
-        <v>90867</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,25 +2590,33 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4366</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
@@ -2742,13 +2625,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523209</v>
+        <v>523346</v>
       </c>
       <c r="R20" t="n">
-        <v>6619782</v>
+        <v>6619799</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2772,12 +2655,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2805,15 +2688,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112280453</v>
+        <v>111350581</v>
       </c>
       <c r="B21" t="n">
-        <v>89558</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2838,8 +2716,16 @@
           <t>(Schwein.) Murrill</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
@@ -2848,13 +2734,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523154</v>
+        <v>523217</v>
       </c>
       <c r="R21" t="n">
-        <v>6619779</v>
+        <v>6619742</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2878,12 +2764,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-09-09</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2911,15 +2797,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112280122</v>
+        <v>111350596</v>
       </c>
       <c r="B22" t="n">
-        <v>90876</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2927,25 +2808,33 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5964</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -2954,13 +2843,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523356</v>
+        <v>523363</v>
       </c>
       <c r="R22" t="n">
-        <v>6619775</v>
+        <v>6619483</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2984,12 +2873,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-08-03</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-09-13</t>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>För ovanlighets skull på stående gran.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3017,15 +2911,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112299360</v>
+        <v>112280423</v>
       </c>
       <c r="B23" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3033,28 +2922,24 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
@@ -3064,10 +2949,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523134</v>
+        <v>523152</v>
       </c>
       <c r="R23" t="n">
-        <v>6619885</v>
+        <v>6619795</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3127,15 +3012,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112280423</v>
+        <v>112280453</v>
       </c>
       <c r="B24" t="n">
-        <v>89558</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3170,10 +3050,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523152</v>
+        <v>523154</v>
       </c>
       <c r="R24" t="n">
-        <v>6619795</v>
+        <v>6619779</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3233,37 +3113,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112299974</v>
+        <v>112299094</v>
       </c>
       <c r="B25" t="n">
-        <v>90878</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3276,10 +3151,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523323</v>
+        <v>523332</v>
       </c>
       <c r="R25" t="n">
-        <v>6619602</v>
+        <v>6619814</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3306,12 +3181,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2023-09-22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3339,15 +3214,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112299188</v>
+        <v>112279968</v>
       </c>
       <c r="B26" t="n">
-        <v>90878</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3355,21 +3225,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3382,10 +3252,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523355</v>
+        <v>523344</v>
       </c>
       <c r="R26" t="n">
-        <v>6619797</v>
+        <v>6619785</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3445,64 +3315,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119371856</v>
+        <v>112280391</v>
       </c>
       <c r="B27" t="n">
-        <v>91859</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1440</v>
+        <v>5448</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brödtaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum versipelle</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bornsviken, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>523350</v>
+        <v>523136</v>
       </c>
       <c r="R27" t="n">
-        <v>6619533</v>
+        <v>6619879</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3529,22 +3383,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>17:29</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>17:29</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3553,6 +3397,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3571,55 +3416,37 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>115775389</v>
+        <v>112280420</v>
       </c>
       <c r="B28" t="n">
-        <v>57220</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103060</v>
+        <v>5754</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brun glada</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Milvus migrans</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3627,10 +3454,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523374</v>
+        <v>523148</v>
       </c>
       <c r="R28" t="n">
-        <v>6619501</v>
+        <v>6619802</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3657,27 +3484,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Sträckte norrut</t>
+          <t>2023-09-09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3686,6 +3498,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3704,15 +3517,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121150986</v>
+        <v>111940426</v>
       </c>
       <c r="B29" t="n">
-        <v>90713</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3720,41 +3528,48 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>5964</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Morskoga, Vstm</t>
+          <t>Bornsviken, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523153</v>
+        <v>523334</v>
       </c>
       <c r="R29" t="n">
-        <v>6619792</v>
+        <v>6619818</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3778,17 +3593,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2023-09-06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3797,21 +3607,1304 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>112280122</v>
+      </c>
+      <c r="B30" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>523356</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6619775</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-09-13</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>112280307</v>
+      </c>
+      <c r="B31" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>523247</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6619802</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ring</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>112280064</v>
+      </c>
+      <c r="B32" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>523388</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6619773</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>112280522</v>
+      </c>
+      <c r="B33" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>523323</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6619602</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>112299188</v>
+      </c>
+      <c r="B34" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>523355</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6619797</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2023-09-22</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>119371589</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>523305</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6619720</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>111744446</v>
+      </c>
+      <c r="B36" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>523374</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6619501</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2023-04-08</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2023-04-08</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>111660462</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>523292</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6619874</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>119371494</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>523309</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6619735</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-08-27</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>121150984</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Morskoga, Vstm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>523349</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6619695</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
+      <c r="AX39" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>111660445</v>
+      </c>
+      <c r="B40" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>523338</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6619822</v>
+      </c>
+      <c r="S40" t="n">
+        <v>25</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2023-08-03</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>112280469</v>
+      </c>
+      <c r="B41" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Bornsviken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>523208</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6619697</v>
+      </c>
+      <c r="S41" t="n">
+        <v>25</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ramsberg</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2023-09-23</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Per Ahlqvist</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42635-2025 artfynd.xlsx
+++ b/artfynd/A 42635-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111929377</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111286442</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150986</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112792336</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119371856</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103464256</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1420,6 +1455,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111660362</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1526,6 +1566,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111660401</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280400</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1736,6 +1786,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280409</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1837,6 +1892,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111658509</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1938,6 +1998,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280348</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2047,6 +2112,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112279685</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2156,6 +2226,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112279929</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2257,6 +2332,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280330</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2366,6 +2446,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112792203</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2467,6 +2552,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111658400</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2576,6 +2666,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350516</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2685,6 +2780,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350555</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2794,6 +2894,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350581</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2908,6 +3013,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111350596</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3009,6 +3119,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280423</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3110,6 +3225,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280453</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3211,6 +3331,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299094</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3312,6 +3437,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112279968</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3413,6 +3543,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280391</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3514,6 +3649,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280420</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3623,6 +3763,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111940426</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3724,6 +3869,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280122</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3838,6 +3988,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280307</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3939,6 +4094,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280064</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4040,6 +4200,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280522</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4141,6 +4306,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112299188</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4258,6 +4428,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119371589</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4371,6 +4546,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111744446</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4473,6 +4653,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111660462</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4587,6 +4772,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119371494</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4693,6 +4883,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121150984</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4795,6 +4990,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111660445</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4905,8 +5105,55 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112280469</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>